--- a/Checklist/Mobile App/Mobile  v1.30.xlsx
+++ b/Checklist/Mobile App/Mobile  v1.30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mberrutto\Documents\GitHub\PentestResources\Checklist\Mobile App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2020A426-21C9-472F-8F64-D203FD099FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EAE02B-4696-4A63-9124-913A09C35FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API" sheetId="6" r:id="rId1"/>
@@ -26,7 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
   <si>
     <t>Weak input validation</t>
   </si>
@@ -421,6 +426,68 @@
   </si>
   <si>
     <t>Password Lack of Complexity</t>
+  </si>
+  <si>
+    <t>UIFileSharingEnabled</t>
+  </si>
+  <si>
+    <t>Sensitive information in source code</t>
+  </si>
+  <si>
+    <t>class-dump -H Diva.app/Diva -o Headers</t>
+  </si>
+  <si>
+    <t>Ver info.plist</t>
+  </si>
+  <si>
+    <t>Binary encrypted</t>
+  </si>
+  <si>
+    <t>otool -l DVIA-v2 | grep -A 5 LC_ENCRYPTION_INFO_64</t>
+  </si>
+  <si>
+    <t>otool -hv Diva.app/Diva</t>
+  </si>
+  <si>
+    <t>Insecure Data Storage</t>
+  </si>
+  <si>
+    <t>Hardcoded Credentials</t>
+  </si>
+  <si>
+    <t>Identify hardcoded secrets in strings: NSString *apiKey = @"sk_test_12345";</t>
+  </si>
+  <si>
+    <t>Check if sensitive data is stored in NSUserDefaults:
+[[NSUserDefaults standardUserDefaults] setObject:@"admin" forKey:@"password"];</t>
+  </si>
+  <si>
+    <t>Weak Cryptographic Functions</t>
+  </si>
+  <si>
+    <t>Debug Flags</t>
+  </si>
+  <si>
+    <t>otool -Iv Diva.app/Diva | grep -i debug</t>
+  </si>
+  <si>
+    <t>Insecure Functions</t>
+  </si>
+  <si>
+    <t>otool -Iv DVIA-v2.app/DVIA-v2 | grep -w "_CC_SHA1"
+otool -Iv DVIA-v2.app/DVIA-v2 | grep -w "_CC_MD5"</t>
+  </si>
+  <si>
+    <t>otool -Iv DVIA-v2.app/DVIA-v2 | grep -E "strcpy|strcat|gets|sprintf|vsprintf|scanf"</t>
+  </si>
+  <si>
+    <t>install inn jaiblreak device</t>
+  </si>
+  <si>
+    <t>Check if you can copy passwords, usernames, etc.</t>
+  </si>
+  <si>
+    <t>Switch the app and see if an screenshot is taken.</t>
   </si>
 </sst>
 </file>
@@ -557,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -588,6 +655,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2355,44 +2423,126 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF737081-1C33-4F47-94AB-23BF72D261C4}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="66" customWidth="1"/>
+    <col min="2" max="2" width="120.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="15"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B3" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="B4" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="B5" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>123</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
